--- a/database/seeders/data/pre_registered_users.xlsx
+++ b/database/seeders/data/pre_registered_users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBD9184-0D45-427F-BD7D-5CBC2707105B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123BD520-A8AD-4090-990E-1C0443DE922C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7335" yWindow="-105" windowWidth="21585" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1290" windowWidth="21585" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Memebers" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2572" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2634" uniqueCount="913">
   <si>
     <t>Status</t>
   </si>
@@ -2783,7 +2783,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2819,6 +2819,13 @@
       <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2861,10 +2868,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2889,8 +2897,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -10659,11 +10669,13 @@
       </c>
     </row>
     <row r="378" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A378" s="10"/>
+      <c r="A378" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B378" s="7" t="s">
         <v>789</v>
       </c>
-      <c r="C378" s="12" t="s">
+      <c r="C378" s="14" t="s">
         <v>851</v>
       </c>
       <c r="D378" s="7" t="s">
@@ -10677,7 +10689,9 @@
       </c>
     </row>
     <row r="379" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A379" s="10"/>
+      <c r="A379" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B379" s="7" t="s">
         <v>790</v>
       </c>
@@ -10695,7 +10709,9 @@
       </c>
     </row>
     <row r="380" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A380" s="10"/>
+      <c r="A380" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B380" s="7" t="s">
         <v>791</v>
       </c>
@@ -10713,7 +10729,9 @@
       </c>
     </row>
     <row r="381" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A381" s="10"/>
+      <c r="A381" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B381" s="7" t="s">
         <v>792</v>
       </c>
@@ -10731,7 +10749,9 @@
       </c>
     </row>
     <row r="382" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A382" s="10"/>
+      <c r="A382" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B382" s="7" t="s">
         <v>793</v>
       </c>
@@ -10749,7 +10769,9 @@
       </c>
     </row>
     <row r="383" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A383" s="10"/>
+      <c r="A383" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B383" s="7" t="s">
         <v>794</v>
       </c>
@@ -10767,7 +10789,9 @@
       </c>
     </row>
     <row r="384" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A384" s="10"/>
+      <c r="A384" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B384" s="7" t="s">
         <v>795</v>
       </c>
@@ -10785,7 +10809,9 @@
       </c>
     </row>
     <row r="385" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A385" s="10"/>
+      <c r="A385" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B385" s="7" t="s">
         <v>796</v>
       </c>
@@ -10803,7 +10829,9 @@
       </c>
     </row>
     <row r="386" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A386" s="10"/>
+      <c r="A386" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B386" s="7" t="s">
         <v>797</v>
       </c>
@@ -10821,7 +10849,9 @@
       </c>
     </row>
     <row r="387" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A387" s="10"/>
+      <c r="A387" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B387" s="7" t="s">
         <v>798</v>
       </c>
@@ -10839,7 +10869,9 @@
       </c>
     </row>
     <row r="388" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A388" s="10"/>
+      <c r="A388" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B388" s="7" t="s">
         <v>799</v>
       </c>
@@ -10857,7 +10889,9 @@
       </c>
     </row>
     <row r="389" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A389" s="10"/>
+      <c r="A389" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B389" s="7" t="s">
         <v>800</v>
       </c>
@@ -10875,7 +10909,9 @@
       </c>
     </row>
     <row r="390" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A390" s="10"/>
+      <c r="A390" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B390" s="7" t="s">
         <v>801</v>
       </c>
@@ -10893,7 +10929,9 @@
       </c>
     </row>
     <row r="391" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A391" s="10"/>
+      <c r="A391" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B391" s="7" t="s">
         <v>802</v>
       </c>
@@ -10911,7 +10949,9 @@
       </c>
     </row>
     <row r="392" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A392" s="10"/>
+      <c r="A392" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B392" s="7" t="s">
         <v>803</v>
       </c>
@@ -10929,7 +10969,9 @@
       </c>
     </row>
     <row r="393" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A393" s="10"/>
+      <c r="A393" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B393" s="7" t="s">
         <v>804</v>
       </c>
@@ -10947,7 +10989,9 @@
       </c>
     </row>
     <row r="394" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A394" s="10"/>
+      <c r="A394" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B394" s="7" t="s">
         <v>805</v>
       </c>
@@ -10965,7 +11009,9 @@
       </c>
     </row>
     <row r="395" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A395" s="10"/>
+      <c r="A395" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B395" s="7" t="s">
         <v>806</v>
       </c>
@@ -10983,7 +11029,9 @@
       </c>
     </row>
     <row r="396" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A396" s="10"/>
+      <c r="A396" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B396" s="7" t="s">
         <v>807</v>
       </c>
@@ -11001,7 +11049,9 @@
       </c>
     </row>
     <row r="397" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A397" s="10"/>
+      <c r="A397" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B397" s="7" t="s">
         <v>808</v>
       </c>
@@ -11019,7 +11069,9 @@
       </c>
     </row>
     <row r="398" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A398" s="10"/>
+      <c r="A398" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B398" s="7" t="s">
         <v>809</v>
       </c>
@@ -11037,7 +11089,9 @@
       </c>
     </row>
     <row r="399" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A399" s="10"/>
+      <c r="A399" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B399" s="7" t="s">
         <v>810</v>
       </c>
@@ -11055,7 +11109,9 @@
       </c>
     </row>
     <row r="400" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A400" s="10"/>
+      <c r="A400" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B400" s="7" t="s">
         <v>811</v>
       </c>
@@ -11073,7 +11129,9 @@
       </c>
     </row>
     <row r="401" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A401" s="10"/>
+      <c r="A401" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B401" s="7" t="s">
         <v>812</v>
       </c>
@@ -11091,7 +11149,9 @@
       </c>
     </row>
     <row r="402" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A402" s="10"/>
+      <c r="A402" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B402" s="7" t="s">
         <v>813</v>
       </c>
@@ -11109,7 +11169,9 @@
       </c>
     </row>
     <row r="403" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A403" s="10"/>
+      <c r="A403" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B403" s="7" t="s">
         <v>814</v>
       </c>
@@ -11127,7 +11189,9 @@
       </c>
     </row>
     <row r="404" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A404" s="10"/>
+      <c r="A404" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B404" s="7" t="s">
         <v>815</v>
       </c>
@@ -11145,7 +11209,9 @@
       </c>
     </row>
     <row r="405" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A405" s="10"/>
+      <c r="A405" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B405" s="7" t="s">
         <v>816</v>
       </c>
@@ -11163,7 +11229,9 @@
       </c>
     </row>
     <row r="406" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A406" s="10"/>
+      <c r="A406" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B406" s="7" t="s">
         <v>817</v>
       </c>
@@ -11181,7 +11249,9 @@
       </c>
     </row>
     <row r="407" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A407" s="10"/>
+      <c r="A407" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B407" s="7" t="s">
         <v>818</v>
       </c>
@@ -11199,7 +11269,9 @@
       </c>
     </row>
     <row r="408" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A408" s="10"/>
+      <c r="A408" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B408" s="7" t="s">
         <v>819</v>
       </c>
@@ -11217,7 +11289,9 @@
       </c>
     </row>
     <row r="409" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A409" s="10"/>
+      <c r="A409" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B409" s="7" t="s">
         <v>820</v>
       </c>
@@ -11235,7 +11309,9 @@
       </c>
     </row>
     <row r="410" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A410" s="10"/>
+      <c r="A410" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B410" s="7" t="s">
         <v>821</v>
       </c>
@@ -11253,7 +11329,9 @@
       </c>
     </row>
     <row r="411" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A411" s="10"/>
+      <c r="A411" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B411" s="7" t="s">
         <v>822</v>
       </c>
@@ -11271,7 +11349,9 @@
       </c>
     </row>
     <row r="412" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A412" s="10"/>
+      <c r="A412" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B412" s="7" t="s">
         <v>823</v>
       </c>
@@ -11289,7 +11369,9 @@
       </c>
     </row>
     <row r="413" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A413" s="10"/>
+      <c r="A413" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B413" s="7" t="s">
         <v>824</v>
       </c>
@@ -11307,7 +11389,9 @@
       </c>
     </row>
     <row r="414" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A414" s="10"/>
+      <c r="A414" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B414" s="7" t="s">
         <v>825</v>
       </c>
@@ -11325,7 +11409,9 @@
       </c>
     </row>
     <row r="415" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A415" s="10"/>
+      <c r="A415" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B415" s="7" t="s">
         <v>826</v>
       </c>
@@ -11343,7 +11429,9 @@
       </c>
     </row>
     <row r="416" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A416" s="10"/>
+      <c r="A416" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B416" s="7" t="s">
         <v>827</v>
       </c>
@@ -11361,7 +11449,9 @@
       </c>
     </row>
     <row r="417" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A417" s="10"/>
+      <c r="A417" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B417" s="7" t="s">
         <v>828</v>
       </c>
@@ -11379,7 +11469,9 @@
       </c>
     </row>
     <row r="418" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A418" s="10"/>
+      <c r="A418" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B418" s="7" t="s">
         <v>829</v>
       </c>
@@ -11397,7 +11489,9 @@
       </c>
     </row>
     <row r="419" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A419" s="10"/>
+      <c r="A419" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B419" s="7" t="s">
         <v>830</v>
       </c>
@@ -11415,7 +11509,9 @@
       </c>
     </row>
     <row r="420" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A420" s="10"/>
+      <c r="A420" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B420" s="7" t="s">
         <v>831</v>
       </c>
@@ -11433,7 +11529,9 @@
       </c>
     </row>
     <row r="421" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A421" s="10"/>
+      <c r="A421" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B421" s="7" t="s">
         <v>832</v>
       </c>
@@ -11451,7 +11549,9 @@
       </c>
     </row>
     <row r="422" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A422" s="10"/>
+      <c r="A422" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B422" s="7" t="s">
         <v>833</v>
       </c>
@@ -11469,7 +11569,9 @@
       </c>
     </row>
     <row r="423" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A423" s="10"/>
+      <c r="A423" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B423" s="7" t="s">
         <v>834</v>
       </c>
@@ -11487,7 +11589,9 @@
       </c>
     </row>
     <row r="424" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A424" s="10"/>
+      <c r="A424" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B424" s="7" t="s">
         <v>835</v>
       </c>
@@ -11505,7 +11609,9 @@
       </c>
     </row>
     <row r="425" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A425" s="10"/>
+      <c r="A425" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B425" s="7" t="s">
         <v>836</v>
       </c>
@@ -11523,7 +11629,9 @@
       </c>
     </row>
     <row r="426" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A426" s="10"/>
+      <c r="A426" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B426" s="7" t="s">
         <v>837</v>
       </c>
@@ -11541,7 +11649,9 @@
       </c>
     </row>
     <row r="427" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A427" s="10"/>
+      <c r="A427" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B427" s="7" t="s">
         <v>838</v>
       </c>
@@ -11559,7 +11669,9 @@
       </c>
     </row>
     <row r="428" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A428" s="10"/>
+      <c r="A428" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B428" s="7" t="s">
         <v>839</v>
       </c>
@@ -11577,7 +11689,9 @@
       </c>
     </row>
     <row r="429" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A429" s="10"/>
+      <c r="A429" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B429" s="7" t="s">
         <v>840</v>
       </c>
@@ -11595,7 +11709,9 @@
       </c>
     </row>
     <row r="430" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A430" s="10"/>
+      <c r="A430" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B430" s="7" t="s">
         <v>841</v>
       </c>
@@ -11613,7 +11729,9 @@
       </c>
     </row>
     <row r="431" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A431" s="10"/>
+      <c r="A431" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B431" s="7" t="s">
         <v>842</v>
       </c>
@@ -11631,7 +11749,9 @@
       </c>
     </row>
     <row r="432" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A432" s="10"/>
+      <c r="A432" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B432" s="7" t="s">
         <v>843</v>
       </c>
@@ -11649,7 +11769,9 @@
       </c>
     </row>
     <row r="433" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A433" s="10"/>
+      <c r="A433" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B433" s="7" t="s">
         <v>844</v>
       </c>
@@ -11667,7 +11789,9 @@
       </c>
     </row>
     <row r="434" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A434" s="10"/>
+      <c r="A434" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B434" s="7" t="s">
         <v>845</v>
       </c>
@@ -11685,7 +11809,9 @@
       </c>
     </row>
     <row r="435" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A435" s="10"/>
+      <c r="A435" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B435" s="7" t="s">
         <v>846</v>
       </c>
@@ -11703,7 +11829,9 @@
       </c>
     </row>
     <row r="436" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A436" s="10"/>
+      <c r="A436" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B436" s="7" t="s">
         <v>847</v>
       </c>
@@ -11721,7 +11849,9 @@
       </c>
     </row>
     <row r="437" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A437" s="10"/>
+      <c r="A437" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B437" s="7" t="s">
         <v>848</v>
       </c>
@@ -11739,7 +11869,9 @@
       </c>
     </row>
     <row r="438" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A438" s="10"/>
+      <c r="A438" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B438" s="7" t="s">
         <v>849</v>
       </c>
@@ -11757,7 +11889,9 @@
       </c>
     </row>
     <row r="439" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A439" s="10"/>
+      <c r="A439" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B439" s="7" t="s">
         <v>850</v>
       </c>
@@ -12210,7 +12344,7 @@
   <customSheetViews>
     <customSheetView guid="{39C0334D-22A1-42C4-B78B-37B934249DD7}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="C1:E493" xr:uid="{AE90F9B6-8125-47DE-BF2E-B6960EE85CFF}">
+      <autoFilter ref="C1:E493" xr:uid="{F4B29D87-AFDF-4932-96CE-1E21B88B67D1}">
         <filterColumn colId="1">
           <filters blank="1">
             <filter val="DESIGN DEPARTMENT"/>
@@ -12222,7 +12356,7 @@
     </customSheetView>
   </customSheetViews>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A377" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A439" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Active,Pause,Stop"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D439" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -12237,6 +12371,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C60" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C378" r:id="rId2" xr:uid="{A5F12DE0-F856-448A-8285-B3773D425EEF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/database/seeders/data/pre_registered_users.xlsx
+++ b/database/seeders/data/pre_registered_users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123BD520-A8AD-4090-990E-1C0443DE922C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AADDBB-0B06-4198-91BF-BBD099CECA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1290" windowWidth="21585" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2783,7 +2783,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2819,13 +2819,6 @@
       <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2868,9 +2861,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2897,10 +2889,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -12344,7 +12335,7 @@
   <customSheetViews>
     <customSheetView guid="{39C0334D-22A1-42C4-B78B-37B934249DD7}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="C1:E493" xr:uid="{F4B29D87-AFDF-4932-96CE-1E21B88B67D1}">
+      <autoFilter ref="C1:E493" xr:uid="{13A3B3D0-8DEC-4266-B461-6B8F278E64FF}">
         <filterColumn colId="1">
           <filters blank="1">
             <filter val="DESIGN DEPARTMENT"/>
@@ -12371,7 +12362,6 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C60" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C378" r:id="rId2" xr:uid="{A5F12DE0-F856-448A-8285-B3773D425EEF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
